--- a/feedback_surveys/024_tripod_product_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/024_tripod_product_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,8 +1083,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'quality_issues'}</t>
+          <t>quality_issues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Quality Issues'}</t>
+          <t>Quality Issues</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'functionality_issues'}</t>
+          <t>functionality_issues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Functionality Issues'}</t>
+          <t>Functionality Issues</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'design_issues'}</t>
+          <t>design_issues</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Design Issues'}</t>
+          <t>Design Issues</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'not_enough_features'}</t>
+          <t>not_enough_features</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Not Enough Features'}</t>
+          <t>Not Enough Features</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'macOS'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'camera'}</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Camera'}</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'monitor'}</t>
+          <t>monitor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Monitor'}</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'tripod'}</t>
+          <t>tripod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Tripod'}</t>
+          <t>Tripod</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
